--- a/inputs/acceptance_cases/stage2_flex_band_accept_baseline.xlsx
+++ b/inputs/acceptance_cases/stage2_flex_band_accept_baseline.xlsx
@@ -465,7 +465,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -493,7 +493,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -507,7 +507,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -521,7 +521,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -535,7 +535,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -549,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -577,7 +577,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -644,10 +644,10 @@
         <v>44569.42708333334</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -658,10 +658,10 @@
         <v>44569.4375</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>32.99999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>32.99999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -675,7 +675,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -703,7 +703,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -829,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -843,7 +843,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -913,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -955,7 +955,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -966,7 +966,7 @@
         <v>44569.41666666666</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D38" t="n">
         <v>33</v>
@@ -980,7 +980,7 @@
         <v>44569.42708333334</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D39" t="n">
         <v>33</v>
@@ -994,7 +994,7 @@
         <v>44569.4375</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D40" t="n">
         <v>33</v>
@@ -1008,10 +1008,10 @@
         <v>44569.44791666666</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>32.99999999999996</v>
       </c>
       <c r="D41" t="n">
-        <v>33</v>
+        <v>32.99999999999996</v>
       </c>
     </row>
     <row r="42">
@@ -1025,7 +1025,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1039,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1193,7 +1193,7 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1221,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1302,7 +1302,7 @@
         <v>44569.41666666666</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D62" t="n">
         <v>33</v>
@@ -1316,10 +1316,10 @@
         <v>44569.42708333334</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D63" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64">
@@ -1330,7 +1330,7 @@
         <v>44569.4375</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D64" t="n">
         <v>33</v>
@@ -1344,10 +1344,10 @@
         <v>44569.44791666666</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>32.99999999999996</v>
       </c>
       <c r="D65" t="n">
-        <v>33</v>
+        <v>32.99999999999996</v>
       </c>
     </row>
     <row r="66">
@@ -1361,7 +1361,7 @@
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
